--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487510_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487510_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.575200000000001</v>
+        <v>7.4249</v>
       </c>
       <c r="E2" t="n">
-        <v>7.6957</v>
+        <v>7.4811</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8794</v>
+        <v>-0.0561</v>
       </c>
       <c r="G2" t="n">
         <v>-0.2136</v>
@@ -610,13 +610,13 @@
         <v>2.7419</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2227</v>
+        <v>2.0724</v>
       </c>
       <c r="T2" t="n">
-        <v>1.475</v>
+        <v>1.2604</v>
       </c>
       <c r="U2" t="n">
-        <v>1.7477</v>
+        <v>0.8121</v>
       </c>
       <c r="V2" t="n">
         <v>3.8035</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2777</v>
+        <v>3.5557</v>
       </c>
       <c r="E3" t="n">
-        <v>4.211</v>
+        <v>3.4088</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0667</v>
+        <v>0.1469</v>
       </c>
       <c r="G3" t="n">
         <v>-1.034</v>
@@ -688,13 +688,13 @@
         <v>2.1543</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3313</v>
+        <v>1.6093</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7368</v>
+        <v>0.9345</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5946</v>
+        <v>0.6747</v>
       </c>
       <c r="V3" t="n">
         <v>0.8260999999999999</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. OGUNFOLU</t>
+          <t>M. FERNANDEZ GIL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3593</v>
+        <v>0.8531</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8425</v>
+        <v>0.8589</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4831</v>
+        <v>-0.0058</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.4631</v>
+        <v>-0.0815</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6737</v>
+        <v>-0.1623</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.1368</v>
+        <v>0.0808</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.0673</v>
+        <v>0.6519</v>
       </c>
       <c r="K4" t="n">
-        <v>1.2164</v>
+        <v>0.0408</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.2836</v>
+        <v>0.611</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3958</v>
+        <v>-0.7333</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5427</v>
+        <v>-0.2031</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1468</v>
+        <v>-0.5302</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9792</v>
+        <v>0.7834</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9792</v>
+        <v>0.7834</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0409</v>
+        <v>-0.297</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0433</v>
+        <v>0.207</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.0025</v>
+        <v>-0.504</v>
       </c>
       <c r="V4" t="n">
-        <v>1.7608</v>
+        <v>0.4481</v>
       </c>
       <c r="W4" t="n">
-        <v>1.8249</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.0641</v>
+        <v>0.4481</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. FERNANDEZ GIL</t>
+          <t>E. OGUNFOLU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2774</v>
+        <v>0.1595</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3902</v>
+        <v>0.509</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1128</v>
+        <v>-0.3495</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0815</v>
+        <v>-0.4631</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1623</v>
+        <v>0.6737</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0808</v>
+        <v>-1.1368</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6519</v>
+        <v>-0.0673</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0408</v>
+        <v>1.2164</v>
       </c>
       <c r="L5" t="n">
-        <v>0.611</v>
+        <v>-1.2836</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7333</v>
+        <v>-0.3958</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2031</v>
+        <v>-0.5427</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5302</v>
+        <v>0.1468</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7834</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7834</v>
+        <v>0.9792</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8727</v>
+        <v>-0.1589</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2617</v>
+        <v>0.7099</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.611</v>
+        <v>-0.8688</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4481</v>
+        <v>1.7608</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.8249</v>
       </c>
       <c r="X5" t="n">
-        <v>0.4481</v>
+        <v>-0.0641</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>É. PINA HURTADO</t>
+          <t>M. RODRIGUEZ ALVAREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.9794</v>
+        <v>-1.77</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6012</v>
+        <v>-0.423</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3783</v>
+        <v>-1.347</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.9143</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9595</v>
+        <v>0.0408</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9548</v>
+        <v>-0.1313</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.182</v>
+        <v>1.7179</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.621</v>
+        <v>0.3793</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5610000000000001</v>
+        <v>1.3385</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7323</v>
+        <v>-1.8083</v>
       </c>
       <c r="N6" t="n">
         <v>-0.3385</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3938</v>
+        <v>-1.4698</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.7834</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9792</v>
+        <v>-2.9377</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1958</v>
+        <v>1.7626</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7181999999999999</v>
+        <v>0.3792</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3435</v>
+        <v>0.7969000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3748</v>
+        <v>-0.4177</v>
       </c>
       <c r="V6" t="n">
+        <v>-0.8837</v>
+      </c>
+      <c r="W6" t="n">
         <v>0</v>
       </c>
-      <c r="W6" t="n">
-        <v>1.2166</v>
-      </c>
       <c r="X6" t="n">
-        <v>-1.2166</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. NIETO GONZALEZ</t>
+          <t>É. PINA HURTADO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.3771</v>
+        <v>-1.9616</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.662</v>
+        <v>-0.423</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7152</v>
+        <v>-1.5387</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2758</v>
+        <v>-1.9143</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8112</v>
+        <v>-0.9595</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5354</v>
+        <v>-0.9548</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6737</v>
+        <v>-1.182</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6737</v>
+        <v>-0.621</v>
       </c>
       <c r="L7" t="n">
+        <v>-0.5610000000000001</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-0.7323</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0.3385</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.3938</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-0.7834</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.9792</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.1958</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.7361</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.5217000000000001</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.2144</v>
+      </c>
+      <c r="V7" t="n">
         <v>0</v>
       </c>
-      <c r="M7" t="n">
-        <v>-0.3979</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.1375</v>
-      </c>
-      <c r="O7" t="n">
-        <v>-0.5354</v>
-      </c>
-      <c r="P7" t="n">
-        <v>-1.5668</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>-1.9585</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.3917</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.1305</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.6228</v>
-      </c>
-      <c r="U7" t="n">
-        <v>-0.4923</v>
-      </c>
-      <c r="V7" t="n">
-        <v>-1.2166</v>
-      </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X7" t="n">
         <v>-1.2166</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. RODRIGUEZ ALVAREZ</t>
+          <t>A. CASAIS ROMERO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.6246</v>
+        <v>-2.353</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.037</v>
+        <v>-0.1936</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5876</v>
+        <v>-2.1594</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.09039999999999999</v>
+        <v>-3.3344</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0408</v>
+        <v>-2.6625</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1313</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7179</v>
+        <v>-0.3865</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3793</v>
+        <v>-1.1689</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3385</v>
+        <v>0.7823</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.8083</v>
+        <v>-2.9478</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3385</v>
+        <v>-1.4936</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.4698</v>
+        <v>-1.4542</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1751</v>
+        <v>2.3502</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9377</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7626</v>
+        <v>2.3502</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4754</v>
+        <v>0.2448</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1829</v>
+        <v>0.1929</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6583</v>
+        <v>0.0519</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.8837</v>
+        <v>-1.6136</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8837</v>
+        <v>-1.6136</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. CASAIS ROMERO</t>
+          <t>J. NIETO GONZALEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.0697</v>
+        <v>-2.7063</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6163</v>
+        <v>-1.0713</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.4534</v>
+        <v>-1.635</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.3344</v>
+        <v>0.2758</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.6625</v>
+        <v>0.8112</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6719000000000001</v>
+        <v>-0.5354</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3865</v>
+        <v>0.6737</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.1689</v>
+        <v>0.6737</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7823</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.9478</v>
+        <v>-0.3979</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4936</v>
+        <v>0.1375</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.4542</v>
+        <v>-0.5354</v>
       </c>
       <c r="P9" t="n">
-        <v>2.3502</v>
+        <v>-1.5668</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3502</v>
+        <v>0.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4719</v>
+        <v>-0.1986</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.2298</v>
+        <v>0.2135</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2421</v>
+        <v>-0.4121</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.6136</v>
+        <v>-1.2166</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.6136</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. CZERAPOWIC</t>
+          <t>C. MONTERO MECA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.122</v>
+        <v>-3.7228</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7595</v>
+        <v>-1.1368</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.3626</v>
+        <v>-2.586</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.6164</v>
+        <v>-0.0794</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4236</v>
+        <v>0.6737</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1928</v>
+        <v>-0.7531</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1404</v>
+        <v>2.6695</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6091</v>
+        <v>1.9632</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4687</v>
+        <v>0.7063</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.476</v>
+        <v>-2.7489</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8145</v>
+        <v>-1.2895</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6615</v>
+        <v>-1.4594</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-2.546</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9585</v>
+        <v>-4.8962</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9585</v>
+        <v>2.3502</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2261</v>
+        <v>1.1245</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0641</v>
+        <v>0.8146</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2902</v>
+        <v>0.31</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.2795</v>
+        <v>-2.2219</v>
       </c>
       <c r="W10" t="n">
         <v>0.2754</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.5549</v>
+        <v>-2.4973</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. MONTERO MECA</t>
+          <t>E. CZERAPOWIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.272</v>
+        <v>-3.9498</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5791</v>
+        <v>-1.6407</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.6929</v>
+        <v>-2.3091</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0794</v>
+        <v>-1.6164</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6737</v>
+        <v>-1.4236</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7531</v>
+        <v>-0.1928</v>
       </c>
       <c r="J11" t="n">
-        <v>2.6695</v>
+        <v>-0.1404</v>
       </c>
       <c r="K11" t="n">
-        <v>1.9632</v>
+        <v>-0.6091</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7063</v>
+        <v>0.4687</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.7489</v>
+        <v>-1.476</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.2895</v>
+        <v>-0.8145</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.4594</v>
+        <v>-0.6615</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.546</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.8962</v>
+        <v>-1.9585</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3502</v>
+        <v>1.9585</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5753</v>
+        <v>-0.0538</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3723</v>
+        <v>0.1829</v>
       </c>
       <c r="U11" t="n">
-        <v>0.203</v>
+        <v>-0.2367</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.2219</v>
+        <v>-2.2795</v>
       </c>
       <c r="W11" t="n">
         <v>0.2754</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.4973</v>
+        <v>-2.5549</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.9552</v>
+        <v>-4.470300000000003</v>
       </c>
       <c r="E12" t="n">
-        <v>5.884300000000001</v>
+        <v>7.369399999999998</v>
       </c>
       <c r="F12" t="n">
-        <v>-11.8398</v>
+        <v>-11.8397</v>
       </c>
       <c r="G12" t="n">
         <v>-8.551299999999999</v>
@@ -1381,7 +1381,7 @@
         <v>-9.9482</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="Q12" t="n">
         <v>-15.6678</v>
@@ -1390,13 +1390,13 @@
         <v>15.6678</v>
       </c>
       <c r="S12" t="n">
-        <v>3.972799999999999</v>
+        <v>5.458000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>4.3492</v>
+        <v>5.834300000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3763000000000001</v>
+        <v>-0.3761999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-1.3768</v>
@@ -1405,7 +1405,7 @@
         <v>8.343599999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-9.720400000000001</v>
+        <v>-9.7204</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.4093</v>
+        <v>9.325699999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>8.383800000000001</v>
+        <v>8.9978</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0254</v>
+        <v>0.3279</v>
       </c>
       <c r="G13" t="n">
         <v>7.1483</v>
@@ -1468,13 +1468,13 @@
         <v>1.9585</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.898</v>
+        <v>-0.9816</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7369</v>
+        <v>-0.1229</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.1611</v>
+        <v>-0.8587</v>
       </c>
       <c r="V13" t="n">
         <v>2.3756</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.9428</v>
+        <v>7.3346</v>
       </c>
       <c r="E14" t="n">
-        <v>6.5405</v>
+        <v>6.3358</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4023</v>
+        <v>0.9988</v>
       </c>
       <c r="G14" t="n">
         <v>3.6519</v>
@@ -1546,13 +1546,13 @@
         <v>1.3709</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7886</v>
+        <v>-0.3968</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0882</v>
+        <v>-0.1165</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8768</v>
+        <v>-0.2804</v>
       </c>
       <c r="V14" t="n">
         <v>2.7086</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.71</v>
+        <v>3.0739</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2021</v>
+        <v>2.4857</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5079</v>
+        <v>0.5881</v>
       </c>
       <c r="G15" t="n">
         <v>1.1692</v>
@@ -1624,13 +1624,13 @@
         <v>1.1751</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2815</v>
+        <v>0.6453</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9487</v>
+        <v>0.2323</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3328</v>
+        <v>0.413</v>
       </c>
       <c r="V15" t="n">
         <v>2.0427</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9787</v>
+        <v>1.1031</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3363</v>
+        <v>0.541</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6424</v>
+        <v>0.5622</v>
       </c>
       <c r="G16" t="n">
         <v>0.2271</v>
@@ -1702,13 +1702,13 @@
         <v>1.5668</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5397999999999999</v>
+        <v>-0.4154</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3564</v>
+        <v>-0.1517</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1834</v>
+        <v>-0.2636</v>
       </c>
       <c r="V16" t="n">
         <v>-0.2754</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4375</v>
+        <v>0.6819</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5596</v>
+        <v>-0.4573</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9971</v>
+        <v>1.1391</v>
       </c>
       <c r="G17" t="n">
         <v>3.2826</v>
@@ -1780,13 +1780,13 @@
         <v>1.9585</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0547</v>
+        <v>0.2991</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2423</v>
+        <v>0.3446</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1876</v>
+        <v>-0.0456</v>
       </c>
       <c r="V17" t="n">
         <v>-0.9412</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1888</v>
+        <v>0.2257</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0847</v>
+        <v>-0.187</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2735</v>
+        <v>0.4127</v>
       </c>
       <c r="G18" t="n">
         <v>-0.119</v>
@@ -1858,13 +1858,13 @@
         <v>2.7419</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3861</v>
+        <v>0.423</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3899</v>
+        <v>0.2876</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0038</v>
+        <v>0.1354</v>
       </c>
       <c r="V18" t="n">
         <v>-0.6659</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2352</v>
+        <v>-0.0481</v>
       </c>
       <c r="E19" t="n">
         <v>0.9417</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1769</v>
+        <v>-0.9898</v>
       </c>
       <c r="G19" t="n">
         <v>0.3319</v>
@@ -1936,13 +1936,13 @@
         <v>1.9585</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7422</v>
+        <v>-0.5551</v>
       </c>
       <c r="T19" t="n">
         <v>-0.0306</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7116</v>
+        <v>-0.5245</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6083</v>
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9654</v>
+        <v>-2.2724</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.175</v>
+        <v>-1.482</v>
       </c>
       <c r="F20" t="n">
         <v>-0.7904</v>
@@ -2014,10 +2014,10 @@
         <v>0.7834</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2311</v>
+        <v>-0.0759</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3852</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="U20" t="n">
         <v>-0.1541</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9425</v>
+        <v>-2.3995</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9097</v>
+        <v>1.3191</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.8523</v>
+        <v>-3.7186</v>
       </c>
       <c r="G21" t="n">
         <v>-2.0669</v>
@@ -2092,13 +2092,13 @@
         <v>0.5875</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.659</v>
+        <v>-0.116</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2023</v>
+        <v>0.207</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4567</v>
+        <v>-0.323</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6083</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3222</v>
+        <v>-2.4676</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.4158</v>
+        <v>-4.2111</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0936</v>
+        <v>1.7435</v>
       </c>
       <c r="G22" t="n">
         <v>-0.7060999999999999</v>
@@ -2170,13 +2170,13 @@
         <v>0.9792</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9906</v>
+        <v>-0.136</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3982</v>
+        <v>-0.1935</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5924</v>
+        <v>0.0575</v>
       </c>
       <c r="V22" t="n">
         <v>0.3329</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.2464</v>
+        <v>-6.5552</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2393</v>
+        <v>-2.444</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.0071</v>
+        <v>-4.1112</v>
       </c>
       <c r="G23" t="n">
         <v>-3.5836</v>
@@ -2248,13 +2248,13 @@
         <v>0.5875</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.308</v>
+        <v>-0.6168</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0465</v>
+        <v>-0.1582</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3545</v>
+        <v>-0.4586</v>
       </c>
       <c r="V23" t="n">
         <v>-1.7673</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>5.9554</v>
+        <v>8.002099999999999</v>
       </c>
       <c r="E24" t="n">
         <v>11.8397</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.884500000000001</v>
+        <v>-3.837699999999999</v>
       </c>
       <c r="G24" t="n">
         <v>8.551299999999999</v>
@@ -2326,13 +2326,13 @@
         <v>15.6678</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.9728</v>
+        <v>-1.9262</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3763999999999998</v>
+        <v>0.3763000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-4.3492</v>
+        <v>-2.3026</v>
       </c>
       <c r="V24" t="n">
         <v>1.3768</v>
